--- a/data/c_Auswertung/energetische_Gebäudesanierung_Auswertung.xlsx
+++ b/data/c_Auswertung/energetische_Gebäudesanierung_Auswertung.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>485802.8394030585</v>
+        <v>482678.7482793811</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>45112.4375</v>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11088.17836006236</v>
+        <v>11087.87333380552</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>45179.16666666666</v>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>204860.2747</v>
+        <v>202592.6925</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>45260.73958333334</v>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-225783.895</v>
+        <v>-223195.858</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>44977.53125</v>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168631.43</v>
+        <v>166497.64</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>44946.375</v>
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-168631.43</v>
+        <v>-166497.64</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>44930.33333333334</v>
+        <v>44930.25</v>
       </c>
     </row>
     <row r="10">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26722.465</v>
+        <v>26268.218</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>44927</v>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-26722.465</v>
+        <v>-26268.218</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>44927.01041666666</v>
